--- a/Tabelas/criterios_por_estado.xlsx
+++ b/Tabelas/criterios_por_estado.xlsx
@@ -515,46 +515,46 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>32.79</v>
+        <v>35.29</v>
       </c>
       <c r="D2" t="n">
-        <v>3.28</v>
+        <v>2.94</v>
       </c>
       <c r="E2" t="n">
-        <v>83.61</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>63.93</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>96.72</v>
+        <v>95.59</v>
       </c>
       <c r="H2" t="n">
-        <v>93.44</v>
+        <v>94.12</v>
       </c>
       <c r="I2" t="n">
-        <v>50.82</v>
+        <v>45.59</v>
       </c>
       <c r="J2" t="n">
-        <v>55.74</v>
+        <v>60.29</v>
       </c>
       <c r="K2" t="n">
-        <v>19.67</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>4.92</v>
+        <v>10.29</v>
       </c>
       <c r="M2" t="n">
-        <v>65.56999999999999</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>16.39</v>
+        <v>22.06</v>
       </c>
       <c r="O2" t="n">
-        <v>59.02</v>
+        <v>54.41</v>
       </c>
       <c r="P2" t="n">
-        <v>98.36</v>
+        <v>97.06</v>
       </c>
     </row>
     <row r="3">
@@ -570,40 +570,40 @@
         <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>21.11</v>
+        <v>20.21</v>
       </c>
       <c r="E3" t="n">
-        <v>82.22</v>
+        <v>82.98</v>
       </c>
       <c r="F3" t="n">
-        <v>62.22</v>
+        <v>62.77</v>
       </c>
       <c r="G3" t="n">
-        <v>96.67</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>94.44</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>73.33</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>54.44</v>
+        <v>54.26</v>
       </c>
       <c r="K3" t="n">
-        <v>7.78</v>
+        <v>9.57</v>
       </c>
       <c r="L3" t="n">
-        <v>3.33</v>
+        <v>3.19</v>
       </c>
       <c r="M3" t="n">
-        <v>72.22</v>
+        <v>71.28</v>
       </c>
       <c r="N3" t="n">
-        <v>13.33</v>
+        <v>15.96</v>
       </c>
       <c r="O3" t="n">
-        <v>70</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="P3" t="n">
         <v>100</v>
@@ -619,46 +619,46 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>31.67</v>
+        <v>32.35</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>58.33</v>
+        <v>61.76</v>
       </c>
       <c r="G4" t="n">
-        <v>96.67</v>
+        <v>97.06</v>
       </c>
       <c r="H4" t="n">
-        <v>70</v>
+        <v>73.53</v>
       </c>
       <c r="I4" t="n">
-        <v>46.67</v>
+        <v>42.65</v>
       </c>
       <c r="J4" t="n">
-        <v>43.33</v>
+        <v>45.59</v>
       </c>
       <c r="K4" t="n">
-        <v>6.67</v>
+        <v>14.71</v>
       </c>
       <c r="L4" t="n">
-        <v>3.33</v>
+        <v>5.88</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>47.06</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>19.12</v>
       </c>
       <c r="O4" t="n">
-        <v>60</v>
+        <v>55.88</v>
       </c>
       <c r="P4" t="n">
-        <v>95</v>
+        <v>95.59</v>
       </c>
     </row>
     <row r="5">
@@ -671,46 +671,46 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>43.75</v>
+        <v>42.37</v>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>10.17</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>79.66</v>
       </c>
       <c r="F5" t="n">
-        <v>70.83</v>
+        <v>71.19</v>
       </c>
       <c r="G5" t="n">
-        <v>93.75</v>
+        <v>89.83</v>
       </c>
       <c r="H5" t="n">
-        <v>95.83</v>
+        <v>96.61</v>
       </c>
       <c r="I5" t="n">
-        <v>45.83</v>
+        <v>37.29</v>
       </c>
       <c r="J5" t="n">
-        <v>56.25</v>
+        <v>52.54</v>
       </c>
       <c r="K5" t="n">
-        <v>29.17</v>
+        <v>33.9</v>
       </c>
       <c r="L5" t="n">
-        <v>4.17</v>
+        <v>6.78</v>
       </c>
       <c r="M5" t="n">
-        <v>64.58</v>
+        <v>61.02</v>
       </c>
       <c r="N5" t="n">
-        <v>14.58</v>
+        <v>22.03</v>
       </c>
       <c r="O5" t="n">
-        <v>54.17</v>
+        <v>49.15</v>
       </c>
       <c r="P5" t="n">
-        <v>93.75</v>
+        <v>94.92</v>
       </c>
     </row>
     <row r="6">
@@ -723,46 +723,46 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>15.75</v>
+        <v>15.99</v>
       </c>
       <c r="D6" t="n">
-        <v>4.72</v>
+        <v>4.46</v>
       </c>
       <c r="E6" t="n">
-        <v>78.73999999999999</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>50.79</v>
+        <v>51.67</v>
       </c>
       <c r="G6" t="n">
-        <v>99.20999999999999</v>
+        <v>98.88</v>
       </c>
       <c r="H6" t="n">
-        <v>87.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>51.18</v>
+        <v>49.44</v>
       </c>
       <c r="J6" t="n">
-        <v>31.89</v>
+        <v>32.71</v>
       </c>
       <c r="K6" t="n">
-        <v>23.62</v>
+        <v>26.02</v>
       </c>
       <c r="L6" t="n">
-        <v>5.12</v>
+        <v>5.2</v>
       </c>
       <c r="M6" t="n">
-        <v>35.04</v>
+        <v>37.17</v>
       </c>
       <c r="N6" t="n">
-        <v>14.17</v>
+        <v>16.36</v>
       </c>
       <c r="O6" t="n">
-        <v>53.94</v>
+        <v>51.3</v>
       </c>
       <c r="P6" t="n">
-        <v>95.28</v>
+        <v>95.54000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -772,49 +772,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="C7" t="n">
-        <v>35.5</v>
+        <v>35.43</v>
       </c>
       <c r="D7" t="n">
-        <v>3.55</v>
+        <v>3.43</v>
       </c>
       <c r="E7" t="n">
-        <v>85.8</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>55.03</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>99.41</v>
+        <v>97.14</v>
       </c>
       <c r="H7" t="n">
-        <v>94.08</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>58.58</v>
+        <v>56.57</v>
       </c>
       <c r="J7" t="n">
-        <v>43.2</v>
+        <v>42.29</v>
       </c>
       <c r="K7" t="n">
-        <v>24.26</v>
+        <v>24</v>
       </c>
       <c r="L7" t="n">
-        <v>8.880000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>56.21</v>
+        <v>55.43</v>
       </c>
       <c r="N7" t="n">
-        <v>20.12</v>
+        <v>22.29</v>
       </c>
       <c r="O7" t="n">
-        <v>57.4</v>
+        <v>55.43</v>
       </c>
       <c r="P7" t="n">
-        <v>94.67</v>
+        <v>94.86</v>
       </c>
     </row>
     <row r="8">
@@ -824,49 +824,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>49.52</v>
+        <v>50.16</v>
       </c>
       <c r="D8" t="n">
-        <v>11.97</v>
+        <v>11.15</v>
       </c>
       <c r="E8" t="n">
-        <v>93.15000000000001</v>
+        <v>93.62</v>
       </c>
       <c r="F8" t="n">
-        <v>74.59</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>96.53</v>
+        <v>96.28</v>
       </c>
       <c r="H8" t="n">
-        <v>92.54000000000001</v>
+        <v>92.97</v>
       </c>
       <c r="I8" t="n">
-        <v>51</v>
+        <v>48.06</v>
       </c>
       <c r="J8" t="n">
-        <v>53.6</v>
+        <v>54.12</v>
       </c>
       <c r="K8" t="n">
-        <v>32.78</v>
+        <v>34.73</v>
       </c>
       <c r="L8" t="n">
-        <v>20.73</v>
+        <v>21.57</v>
       </c>
       <c r="M8" t="n">
-        <v>85.95</v>
+        <v>86.27</v>
       </c>
       <c r="N8" t="n">
-        <v>29.4</v>
+        <v>31.66</v>
       </c>
       <c r="O8" t="n">
-        <v>54.47</v>
+        <v>52.99</v>
       </c>
       <c r="P8" t="n">
-        <v>96.62</v>
+        <v>96.69</v>
       </c>
     </row>
     <row r="9">
@@ -876,49 +876,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>47.09</v>
+        <v>46.33</v>
       </c>
       <c r="D9" t="n">
-        <v>5.23</v>
+        <v>5.08</v>
       </c>
       <c r="E9" t="n">
-        <v>66.28</v>
+        <v>67.23</v>
       </c>
       <c r="F9" t="n">
-        <v>51.16</v>
+        <v>51.98</v>
       </c>
       <c r="G9" t="n">
-        <v>97.67</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>86.05</v>
+        <v>86.44</v>
       </c>
       <c r="I9" t="n">
-        <v>68.59999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J9" t="n">
-        <v>26.74</v>
+        <v>26.55</v>
       </c>
       <c r="K9" t="n">
-        <v>9.880000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="L9" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="M9" t="n">
-        <v>47.67</v>
+        <v>46.89</v>
       </c>
       <c r="N9" t="n">
-        <v>11.05</v>
+        <v>12.99</v>
       </c>
       <c r="O9" t="n">
-        <v>63.37</v>
+        <v>62.15</v>
       </c>
       <c r="P9" t="n">
-        <v>98.84</v>
+        <v>98.87</v>
       </c>
     </row>
     <row r="10">
@@ -931,46 +931,46 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>44.44</v>
+        <v>44.68</v>
       </c>
       <c r="D10" t="n">
-        <v>5.19</v>
+        <v>4.96</v>
       </c>
       <c r="E10" t="n">
-        <v>86.3</v>
+        <v>86.88</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>40.78</v>
       </c>
       <c r="G10" t="n">
-        <v>95.56</v>
+        <v>94.33</v>
       </c>
       <c r="H10" t="n">
-        <v>87.04000000000001</v>
+        <v>87.59</v>
       </c>
       <c r="I10" t="n">
-        <v>56.67</v>
+        <v>54.26</v>
       </c>
       <c r="J10" t="n">
-        <v>34.07</v>
+        <v>34.04</v>
       </c>
       <c r="K10" t="n">
-        <v>18.15</v>
+        <v>19.15</v>
       </c>
       <c r="L10" t="n">
-        <v>2.59</v>
+        <v>2.84</v>
       </c>
       <c r="M10" t="n">
-        <v>43.33</v>
+        <v>44.68</v>
       </c>
       <c r="N10" t="n">
-        <v>10.74</v>
+        <v>13.83</v>
       </c>
       <c r="O10" t="n">
-        <v>53.7</v>
+        <v>53.55</v>
       </c>
       <c r="P10" t="n">
-        <v>99.63</v>
+        <v>99.65000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -983,46 +983,46 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>10.77</v>
+        <v>10.14</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>81.16</v>
       </c>
       <c r="F11" t="n">
-        <v>52.31</v>
+        <v>52.17</v>
       </c>
       <c r="G11" t="n">
-        <v>93.84999999999999</v>
+        <v>89.86</v>
       </c>
       <c r="H11" t="n">
-        <v>92.31</v>
+        <v>92.75</v>
       </c>
       <c r="I11" t="n">
-        <v>55.38</v>
+        <v>52.17</v>
       </c>
       <c r="J11" t="n">
-        <v>29.23</v>
+        <v>27.54</v>
       </c>
       <c r="K11" t="n">
-        <v>16.92</v>
+        <v>15.94</v>
       </c>
       <c r="L11" t="n">
-        <v>3.08</v>
+        <v>5.8</v>
       </c>
       <c r="M11" t="n">
-        <v>40</v>
+        <v>40.58</v>
       </c>
       <c r="N11" t="n">
-        <v>16.92</v>
+        <v>20.29</v>
       </c>
       <c r="O11" t="n">
-        <v>43.08</v>
+        <v>40.58</v>
       </c>
       <c r="P11" t="n">
-        <v>93.84999999999999</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="12">
@@ -1035,46 +1035,46 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>36.41</v>
+        <v>36.34</v>
       </c>
       <c r="D12" t="n">
-        <v>4.75</v>
+        <v>4.64</v>
       </c>
       <c r="E12" t="n">
-        <v>91.56</v>
+        <v>91.75</v>
       </c>
       <c r="F12" t="n">
-        <v>43.01</v>
+        <v>43.81</v>
       </c>
       <c r="G12" t="n">
-        <v>95.78</v>
+        <v>95.62</v>
       </c>
       <c r="H12" t="n">
-        <v>79.95</v>
+        <v>80.41</v>
       </c>
       <c r="I12" t="n">
-        <v>50.92</v>
+        <v>49.74</v>
       </c>
       <c r="J12" t="n">
-        <v>34.3</v>
+        <v>34.28</v>
       </c>
       <c r="K12" t="n">
-        <v>13.98</v>
+        <v>14.69</v>
       </c>
       <c r="L12" t="n">
-        <v>4.22</v>
+        <v>4.38</v>
       </c>
       <c r="M12" t="n">
-        <v>48.81</v>
+        <v>48.97</v>
       </c>
       <c r="N12" t="n">
-        <v>8.44</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>56.2</v>
+        <v>55.67</v>
       </c>
       <c r="P12" t="n">
-        <v>95.25</v>
+        <v>95.36</v>
       </c>
     </row>
     <row r="13">
@@ -1087,46 +1087,46 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43.84</v>
+        <v>44.16</v>
       </c>
       <c r="D13" t="n">
-        <v>15.07</v>
+        <v>14.29</v>
       </c>
       <c r="E13" t="n">
-        <v>80.14</v>
+        <v>81.17</v>
       </c>
       <c r="F13" t="n">
-        <v>56.85</v>
+        <v>57.79</v>
       </c>
       <c r="G13" t="n">
-        <v>93.15000000000001</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>91.09999999999999</v>
+        <v>91.56</v>
       </c>
       <c r="I13" t="n">
-        <v>58.22</v>
+        <v>55.19</v>
       </c>
       <c r="J13" t="n">
-        <v>39.04</v>
+        <v>38.31</v>
       </c>
       <c r="K13" t="n">
-        <v>15.75</v>
+        <v>16.88</v>
       </c>
       <c r="L13" t="n">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="M13" t="n">
-        <v>44.52</v>
+        <v>46.1</v>
       </c>
       <c r="N13" t="n">
-        <v>8.220000000000001</v>
+        <v>11.04</v>
       </c>
       <c r="O13" t="n">
-        <v>52.74</v>
+        <v>51.3</v>
       </c>
       <c r="P13" t="n">
-        <v>99.31999999999999</v>
+        <v>99.34999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1136,49 +1136,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="C14" t="n">
-        <v>32.84</v>
+        <v>31.17</v>
       </c>
       <c r="D14" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="E14" t="n">
-        <v>88.06</v>
+        <v>89.61</v>
       </c>
       <c r="F14" t="n">
-        <v>47.76</v>
+        <v>50.65</v>
       </c>
       <c r="G14" t="n">
-        <v>91.04000000000001</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>95.52</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>49.25</v>
+        <v>42.86</v>
       </c>
       <c r="J14" t="n">
-        <v>44.78</v>
+        <v>42.86</v>
       </c>
       <c r="K14" t="n">
-        <v>28.36</v>
+        <v>28.57</v>
       </c>
       <c r="L14" t="n">
-        <v>17.91</v>
+        <v>16.88</v>
       </c>
       <c r="M14" t="n">
-        <v>56.72</v>
+        <v>54.55</v>
       </c>
       <c r="N14" t="n">
-        <v>22.39</v>
+        <v>24.68</v>
       </c>
       <c r="O14" t="n">
-        <v>55.22</v>
+        <v>48.05</v>
       </c>
       <c r="P14" t="n">
-        <v>95.52</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1191,46 +1191,46 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41.26</v>
+        <v>43.22</v>
       </c>
       <c r="D15" t="n">
-        <v>4.04</v>
+        <v>3.81</v>
       </c>
       <c r="E15" t="n">
-        <v>90.13</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>52.47</v>
+        <v>54.66</v>
       </c>
       <c r="G15" t="n">
-        <v>95.52</v>
+        <v>93.64</v>
       </c>
       <c r="H15" t="n">
-        <v>86.55</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>55.61</v>
+        <v>52.97</v>
       </c>
       <c r="J15" t="n">
-        <v>42.15</v>
+        <v>42.8</v>
       </c>
       <c r="K15" t="n">
-        <v>21.97</v>
+        <v>24.58</v>
       </c>
       <c r="L15" t="n">
-        <v>8.970000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="M15" t="n">
-        <v>46.64</v>
+        <v>48.73</v>
       </c>
       <c r="N15" t="n">
-        <v>11.66</v>
+        <v>13.56</v>
       </c>
       <c r="O15" t="n">
-        <v>52.47</v>
+        <v>50.85</v>
       </c>
       <c r="P15" t="n">
-        <v>96.86</v>
+        <v>97.03</v>
       </c>
     </row>
     <row r="16">
@@ -1243,46 +1243,46 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.85</v>
+        <v>32.67</v>
       </c>
       <c r="D16" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="E16" t="n">
-        <v>80.84999999999999</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>44.68</v>
+        <v>47.52</v>
       </c>
       <c r="G16" t="n">
-        <v>97.87</v>
+        <v>97.03</v>
       </c>
       <c r="H16" t="n">
-        <v>88.3</v>
+        <v>89.11</v>
       </c>
       <c r="I16" t="n">
-        <v>64.89</v>
+        <v>61.39</v>
       </c>
       <c r="J16" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="K16" t="n">
-        <v>14.89</v>
+        <v>17.82</v>
       </c>
       <c r="L16" t="n">
-        <v>4.26</v>
+        <v>4.95</v>
       </c>
       <c r="M16" t="n">
-        <v>46.81</v>
+        <v>47.52</v>
       </c>
       <c r="N16" t="n">
-        <v>18.09</v>
+        <v>23.76</v>
       </c>
       <c r="O16" t="n">
-        <v>63.83</v>
+        <v>61.39</v>
       </c>
       <c r="P16" t="n">
-        <v>94.68000000000001</v>
+        <v>95.05</v>
       </c>
     </row>
     <row r="17">
@@ -1295,46 +1295,46 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>46.1</v>
+        <v>45.94</v>
       </c>
       <c r="D17" t="n">
-        <v>6.69</v>
+        <v>6.36</v>
       </c>
       <c r="E17" t="n">
-        <v>88.09999999999999</v>
+        <v>88.69</v>
       </c>
       <c r="F17" t="n">
-        <v>55.39</v>
+        <v>56.54</v>
       </c>
       <c r="G17" t="n">
-        <v>95.54000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="H17" t="n">
-        <v>91.08</v>
+        <v>91.52</v>
       </c>
       <c r="I17" t="n">
-        <v>60.22</v>
+        <v>57.6</v>
       </c>
       <c r="J17" t="n">
-        <v>51.67</v>
+        <v>52.3</v>
       </c>
       <c r="K17" t="n">
-        <v>22.3</v>
+        <v>24.73</v>
       </c>
       <c r="L17" t="n">
-        <v>9.289999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="M17" t="n">
-        <v>60.22</v>
+        <v>60.42</v>
       </c>
       <c r="N17" t="n">
-        <v>20.82</v>
+        <v>21.91</v>
       </c>
       <c r="O17" t="n">
-        <v>56.88</v>
+        <v>54.77</v>
       </c>
       <c r="P17" t="n">
-        <v>97.03</v>
+        <v>97.17</v>
       </c>
     </row>
     <row r="18">
@@ -1347,46 +1347,46 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>22.01</v>
+        <v>21.59</v>
       </c>
       <c r="D18" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="E18" t="n">
-        <v>94.73999999999999</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>40.19</v>
+        <v>42.73</v>
       </c>
       <c r="G18" t="n">
-        <v>98.09</v>
+        <v>96.48</v>
       </c>
       <c r="H18" t="n">
-        <v>97.61</v>
+        <v>97.8</v>
       </c>
       <c r="I18" t="n">
-        <v>47.85</v>
+        <v>44.49</v>
       </c>
       <c r="J18" t="n">
-        <v>32.54</v>
+        <v>33.48</v>
       </c>
       <c r="K18" t="n">
-        <v>22.01</v>
+        <v>24.23</v>
       </c>
       <c r="L18" t="n">
-        <v>2.39</v>
+        <v>3.52</v>
       </c>
       <c r="M18" t="n">
-        <v>31.58</v>
+        <v>33.48</v>
       </c>
       <c r="N18" t="n">
-        <v>13.4</v>
+        <v>17.18</v>
       </c>
       <c r="O18" t="n">
-        <v>42.58</v>
+        <v>40.53</v>
       </c>
       <c r="P18" t="n">
-        <v>99.04000000000001</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="19">
@@ -1399,46 +1399,46 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.88</v>
+        <v>37.11</v>
       </c>
       <c r="D19" t="n">
-        <v>7.45</v>
+        <v>7.22</v>
       </c>
       <c r="E19" t="n">
-        <v>79.79000000000001</v>
+        <v>80.41</v>
       </c>
       <c r="F19" t="n">
-        <v>48.94</v>
+        <v>50.52</v>
       </c>
       <c r="G19" t="n">
-        <v>98.58</v>
+        <v>97.94</v>
       </c>
       <c r="H19" t="n">
-        <v>93.26000000000001</v>
+        <v>93.47</v>
       </c>
       <c r="I19" t="n">
-        <v>66.67</v>
+        <v>65.64</v>
       </c>
       <c r="J19" t="n">
-        <v>46.81</v>
+        <v>46.74</v>
       </c>
       <c r="K19" t="n">
-        <v>15.6</v>
+        <v>16.49</v>
       </c>
       <c r="L19" t="n">
-        <v>3.55</v>
+        <v>4.12</v>
       </c>
       <c r="M19" t="n">
-        <v>52.13</v>
+        <v>51.89</v>
       </c>
       <c r="N19" t="n">
-        <v>12.77</v>
+        <v>15.12</v>
       </c>
       <c r="O19" t="n">
-        <v>55.32</v>
+        <v>54.64</v>
       </c>
       <c r="P19" t="n">
-        <v>98.94</v>
+        <v>98.97</v>
       </c>
     </row>
     <row r="20">
@@ -1448,49 +1448,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="C20" t="n">
-        <v>49.15</v>
+        <v>49.43</v>
       </c>
       <c r="D20" t="n">
-        <v>3.06</v>
+        <v>2.93</v>
       </c>
       <c r="E20" t="n">
-        <v>83.16</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>55.27</v>
+        <v>56.1</v>
       </c>
       <c r="G20" t="n">
-        <v>96.94</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>89.12</v>
+        <v>89.59</v>
       </c>
       <c r="I20" t="n">
-        <v>54.59</v>
+        <v>52.52</v>
       </c>
       <c r="J20" t="n">
-        <v>50</v>
+        <v>49.11</v>
       </c>
       <c r="K20" t="n">
-        <v>16.84</v>
+        <v>17.24</v>
       </c>
       <c r="L20" t="n">
-        <v>10.54</v>
+        <v>10.73</v>
       </c>
       <c r="M20" t="n">
-        <v>75.68000000000001</v>
+        <v>75.28</v>
       </c>
       <c r="N20" t="n">
-        <v>14.12</v>
+        <v>15.12</v>
       </c>
       <c r="O20" t="n">
-        <v>59.86</v>
+        <v>58.37</v>
       </c>
       <c r="P20" t="n">
-        <v>98.3</v>
+        <v>98.37</v>
       </c>
     </row>
     <row r="21">
@@ -1503,46 +1503,46 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>38.82</v>
+        <v>38.89</v>
       </c>
       <c r="D21" t="n">
-        <v>9.41</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>83.53</v>
+        <v>84.44</v>
       </c>
       <c r="F21" t="n">
-        <v>45.88</v>
+        <v>47.78</v>
       </c>
       <c r="G21" t="n">
-        <v>98.81999999999999</v>
+        <v>98.89</v>
       </c>
       <c r="H21" t="n">
-        <v>90.59</v>
+        <v>91.11</v>
       </c>
       <c r="I21" t="n">
-        <v>55.29</v>
+        <v>52.22</v>
       </c>
       <c r="J21" t="n">
-        <v>38.82</v>
+        <v>40</v>
       </c>
       <c r="K21" t="n">
-        <v>27.06</v>
+        <v>27.78</v>
       </c>
       <c r="L21" t="n">
-        <v>7.06</v>
+        <v>6.67</v>
       </c>
       <c r="M21" t="n">
-        <v>50.59</v>
+        <v>50</v>
       </c>
       <c r="N21" t="n">
-        <v>10.59</v>
+        <v>14.44</v>
       </c>
       <c r="O21" t="n">
-        <v>64.70999999999999</v>
+        <v>62.22</v>
       </c>
       <c r="P21" t="n">
-        <v>96.47</v>
+        <v>96.67</v>
       </c>
     </row>
     <row r="22">
@@ -1555,43 +1555,43 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>37.78</v>
+        <v>36.73</v>
       </c>
       <c r="D22" t="n">
-        <v>17.78</v>
+        <v>16.33</v>
       </c>
       <c r="E22" t="n">
-        <v>91.11</v>
+        <v>91.84</v>
       </c>
       <c r="F22" t="n">
-        <v>55.56</v>
+        <v>57.14</v>
       </c>
       <c r="G22" t="n">
-        <v>100</v>
+        <v>95.92</v>
       </c>
       <c r="H22" t="n">
-        <v>84.44</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>66.67</v>
+        <v>61.22</v>
       </c>
       <c r="J22" t="n">
-        <v>42.22</v>
+        <v>38.78</v>
       </c>
       <c r="K22" t="n">
-        <v>13.33</v>
+        <v>14.29</v>
       </c>
       <c r="L22" t="n">
-        <v>6.67</v>
+        <v>8.16</v>
       </c>
       <c r="M22" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="N22" t="n">
-        <v>13.33</v>
+        <v>18.37</v>
       </c>
       <c r="O22" t="n">
-        <v>68.89</v>
+        <v>63.27</v>
       </c>
       <c r="P22" t="n">
         <v>100</v>
@@ -1607,43 +1607,43 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>32.76</v>
+        <v>32.31</v>
       </c>
       <c r="D23" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="E23" t="n">
-        <v>89.66</v>
+        <v>90.77</v>
       </c>
       <c r="F23" t="n">
-        <v>55.17</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>94.83</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>96.55</v>
+        <v>96.92</v>
       </c>
       <c r="I23" t="n">
-        <v>67.23999999999999</v>
+        <v>60</v>
       </c>
       <c r="J23" t="n">
-        <v>39.66</v>
+        <v>41.54</v>
       </c>
       <c r="K23" t="n">
-        <v>15.52</v>
+        <v>16.92</v>
       </c>
       <c r="L23" t="n">
-        <v>12.07</v>
+        <v>10.77</v>
       </c>
       <c r="M23" t="n">
-        <v>72.41</v>
+        <v>72.31</v>
       </c>
       <c r="N23" t="n">
-        <v>15.52</v>
+        <v>20</v>
       </c>
       <c r="O23" t="n">
-        <v>58.62</v>
+        <v>55.38</v>
       </c>
       <c r="P23" t="n">
         <v>100</v>
@@ -1656,49 +1656,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="C24" t="n">
-        <v>36.11</v>
+        <v>37.11</v>
       </c>
       <c r="D24" t="n">
-        <v>16.11</v>
+        <v>14.95</v>
       </c>
       <c r="E24" t="n">
-        <v>81.67</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>52.22</v>
+        <v>54.12</v>
       </c>
       <c r="G24" t="n">
-        <v>95</v>
+        <v>93.81</v>
       </c>
       <c r="H24" t="n">
-        <v>90.56</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>58.89</v>
+        <v>54.64</v>
       </c>
       <c r="J24" t="n">
-        <v>40</v>
+        <v>40.21</v>
       </c>
       <c r="K24" t="n">
-        <v>13.89</v>
+        <v>13.92</v>
       </c>
       <c r="L24" t="n">
-        <v>5.56</v>
+        <v>5.15</v>
       </c>
       <c r="M24" t="n">
-        <v>47.78</v>
+        <v>48.45</v>
       </c>
       <c r="N24" t="n">
-        <v>9.44</v>
+        <v>11.86</v>
       </c>
       <c r="O24" t="n">
-        <v>62.22</v>
+        <v>58.76</v>
       </c>
       <c r="P24" t="n">
-        <v>99.44</v>
+        <v>99.48</v>
       </c>
     </row>
     <row r="25">
@@ -1708,49 +1708,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="C25" t="n">
-        <v>54.61</v>
+        <v>54.09</v>
       </c>
       <c r="D25" t="n">
-        <v>12.55</v>
+        <v>12.1</v>
       </c>
       <c r="E25" t="n">
-        <v>89.67</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>55.72</v>
+        <v>56.94</v>
       </c>
       <c r="G25" t="n">
-        <v>87.81999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>87.08</v>
+        <v>86.83</v>
       </c>
       <c r="I25" t="n">
-        <v>40.59</v>
+        <v>39.15</v>
       </c>
       <c r="J25" t="n">
-        <v>39.48</v>
+        <v>38.43</v>
       </c>
       <c r="K25" t="n">
-        <v>18.45</v>
+        <v>18.51</v>
       </c>
       <c r="L25" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M25" t="n">
-        <v>52.4</v>
+        <v>53.02</v>
       </c>
       <c r="N25" t="n">
-        <v>11.81</v>
+        <v>12.46</v>
       </c>
       <c r="O25" t="n">
-        <v>47.6</v>
+        <v>46.62</v>
       </c>
       <c r="P25" t="n">
-        <v>97.42</v>
+        <v>97.51000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1760,49 +1760,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="C26" t="n">
-        <v>30.11</v>
+        <v>30.22</v>
       </c>
       <c r="D26" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="E26" t="n">
-        <v>86.36</v>
+        <v>86.81</v>
       </c>
       <c r="F26" t="n">
-        <v>45.45</v>
+        <v>46.7</v>
       </c>
       <c r="G26" t="n">
-        <v>98.86</v>
+        <v>97.25</v>
       </c>
       <c r="H26" t="n">
-        <v>92.05</v>
+        <v>92.31</v>
       </c>
       <c r="I26" t="n">
-        <v>50</v>
+        <v>48.35</v>
       </c>
       <c r="J26" t="n">
-        <v>39.2</v>
+        <v>38.46</v>
       </c>
       <c r="K26" t="n">
-        <v>18.18</v>
+        <v>19.23</v>
       </c>
       <c r="L26" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="M26" t="n">
-        <v>46.02</v>
+        <v>46.7</v>
       </c>
       <c r="N26" t="n">
-        <v>8.52</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>56.25</v>
+        <v>54.4</v>
       </c>
       <c r="P26" t="n">
-        <v>97.73</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="27">
@@ -1812,49 +1812,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="C27" t="n">
-        <v>31.93</v>
+        <v>32.67</v>
       </c>
       <c r="D27" t="n">
-        <v>6.33</v>
+        <v>5.97</v>
       </c>
       <c r="E27" t="n">
-        <v>79.81999999999999</v>
+        <v>80.97</v>
       </c>
       <c r="F27" t="n">
-        <v>37.95</v>
+        <v>40.34</v>
       </c>
       <c r="G27" t="n">
-        <v>99.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="H27" t="n">
-        <v>90.36</v>
+        <v>90.91</v>
       </c>
       <c r="I27" t="n">
-        <v>63.55</v>
+        <v>60.23</v>
       </c>
       <c r="J27" t="n">
-        <v>31.33</v>
+        <v>31.53</v>
       </c>
       <c r="K27" t="n">
-        <v>15.66</v>
+        <v>17.33</v>
       </c>
       <c r="L27" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="M27" t="n">
-        <v>47.29</v>
+        <v>48.58</v>
       </c>
       <c r="N27" t="n">
-        <v>9.34</v>
+        <v>11.08</v>
       </c>
       <c r="O27" t="n">
-        <v>58.13</v>
+        <v>56.53</v>
       </c>
       <c r="P27" t="n">
-        <v>96.98999999999999</v>
+        <v>97.16</v>
       </c>
     </row>
     <row r="28">
@@ -1867,46 +1867,46 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>28.81</v>
+        <v>27.42</v>
       </c>
       <c r="D28" t="n">
-        <v>5.08</v>
+        <v>4.84</v>
       </c>
       <c r="E28" t="n">
-        <v>83.05</v>
+        <v>83.87</v>
       </c>
       <c r="F28" t="n">
-        <v>54.24</v>
+        <v>56.45</v>
       </c>
       <c r="G28" t="n">
-        <v>94.92</v>
+        <v>93.55</v>
       </c>
       <c r="H28" t="n">
-        <v>89.83</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>44.07</v>
+        <v>41.94</v>
       </c>
       <c r="J28" t="n">
-        <v>38.98</v>
+        <v>41.94</v>
       </c>
       <c r="K28" t="n">
-        <v>25.42</v>
+        <v>29.03</v>
       </c>
       <c r="L28" t="n">
-        <v>5.08</v>
+        <v>4.84</v>
       </c>
       <c r="M28" t="n">
-        <v>57.63</v>
+        <v>58.06</v>
       </c>
       <c r="N28" t="n">
-        <v>16.95</v>
+        <v>20.97</v>
       </c>
       <c r="O28" t="n">
-        <v>49.15</v>
+        <v>48.39</v>
       </c>
       <c r="P28" t="n">
-        <v>94.92</v>
+        <v>95.16</v>
       </c>
     </row>
     <row r="29">
@@ -1919,46 +1919,46 @@
         <v>0.29</v>
       </c>
       <c r="C29" t="n">
-        <v>40.48</v>
+        <v>40.71</v>
       </c>
       <c r="D29" t="n">
-        <v>7.44</v>
+        <v>7.03</v>
       </c>
       <c r="E29" t="n">
-        <v>86.06</v>
+        <v>86.84</v>
       </c>
       <c r="F29" t="n">
-        <v>54.92</v>
+        <v>56.44</v>
       </c>
       <c r="G29" t="n">
-        <v>96.40000000000001</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>89.89</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>55.04</v>
+        <v>52.31</v>
       </c>
       <c r="J29" t="n">
-        <v>43.17</v>
+        <v>43.3</v>
       </c>
       <c r="K29" t="n">
-        <v>20.88</v>
+        <v>22.41</v>
       </c>
       <c r="L29" t="n">
-        <v>8.539999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="M29" t="n">
-        <v>59.05</v>
+        <v>59.61</v>
       </c>
       <c r="N29" t="n">
-        <v>16.14</v>
+        <v>18.53</v>
       </c>
       <c r="O29" t="n">
-        <v>55.83</v>
+        <v>54.07</v>
       </c>
       <c r="P29" t="n">
-        <v>97.26000000000001</v>
+        <v>97.36</v>
       </c>
     </row>
   </sheetData>
